--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31765,6 +31765,25 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31784,6 +31784,25 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
         <v>100</v>
       </c>
     </row>
